--- a/figuras/tabela_1.xlsx
+++ b/figuras/tabela_1.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="632">
   <si>
     <t xml:space="preserve">Characteristic
 </t>
@@ -21,7 +21,7 @@
     <t xml:space="preserve">peso_kg</t>
   </si>
   <si>
-    <t xml:space="preserve">     Unknown</t>
+    <t xml:space="preserve">    Unknown</t>
   </si>
   <si>
     <t xml:space="preserve">altura_cm</t>
@@ -36,58 +36,58 @@
     <t xml:space="preserve">cor</t>
   </si>
   <si>
-    <t xml:space="preserve">     amarela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     branca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     indigena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     nao_respondeu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     nao_sabe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     parda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     preta</t>
+    <t xml:space="preserve">    amarela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    branca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    indigena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    nao_respondeu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    nao_sabe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    parda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    preta</t>
   </si>
   <si>
     <t xml:space="preserve">escolaridade_cat_num</t>
   </si>
   <si>
-    <t xml:space="preserve">     0-4 anos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     12 ou mais anos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     5-8 anos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     9-11 anos</t>
+    <t xml:space="preserve">    0-4 anos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    12 ou mais anos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    5-8 anos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    9-11 anos</t>
   </si>
   <si>
     <t xml:space="preserve">macro_reg</t>
   </si>
   <si>
-    <t xml:space="preserve">     Centro-Oeste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     Nordeste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     Norte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     Sudeste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     Sul</t>
+    <t xml:space="preserve">    Centro-Oeste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Nordeste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Norte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Sudeste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Sul</t>
   </si>
   <si>
     <t xml:space="preserve">trabalha</t>
@@ -111,17 +111,18 @@
     <t xml:space="preserve">Mean (SD); n (%)</t>
   </si>
   <si>
-    <t xml:space="preserve">2009, N = 54,367
+    <t xml:space="preserve">2009
+N = 54,367
 </t>
   </si>
   <si>
-    <t xml:space="preserve">69 (15)</t>
+    <t xml:space="preserve">69.0 (14.6)</t>
   </si>
   <si>
     <t xml:space="preserve">1,486</t>
   </si>
   <si>
-    <t xml:space="preserve">165 (10)</t>
+    <t xml:space="preserve">165.1 (9.9)</t>
   </si>
   <si>
     <t xml:space="preserve">3,450</t>
@@ -130,125 +131,126 @@
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">21,347 (39%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33,020 (61%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,760 (14%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10,664 (20%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11,369 (21%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10,238 (19%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,450 (14%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,886 (13%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">211 (0.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21,507 (40%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32 (&lt;0.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57 (0.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67 (0.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29,706 (55%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,787 (5.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,567 (12%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18,144 (33%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,386 (15%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21,203 (39%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,046 (15%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18,122 (33%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16,124 (30%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,040 (11%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,035 (11%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33,811 (62%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20,556 (38%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17,431 (32%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36,878 (68%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58 (0.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18,040 (53%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15,713 (46%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58 (0.2%)</t>
+    <t xml:space="preserve">21,347.0 (39.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33,020.0 (60.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,760.0 (14.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10,664.0 (19.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11,369.0 (20.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10,238.0 (18.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,450.0 (13.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,886.0 (12.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">211.0 (0.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21,507.0 (39.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0 (0.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.0 (0.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.0 (0.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29,706.0 (54.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,787.0 (5.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,567.0 (12.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18,144.0 (33.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,386.0 (15.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21,203.0 (39.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,046.0 (14.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18,122.0 (33.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16,124.0 (29.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,040.0 (11.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,035.0 (11.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33,811.0 (62.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20,556.0 (37.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17,431.0 (32.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36,878.0 (67.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0 (0.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18,040.0 (53.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15,713.0 (46.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0 (0.2%)</t>
   </si>
   <si>
     <t xml:space="preserve">20,556</t>
   </si>
   <si>
-    <t xml:space="preserve">6,810 (20%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,057 (18%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20,944 (62%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,851 (14%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 (18)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2010, N = 54,339
+    <t xml:space="preserve">6,810.0 (20.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,057.0 (17.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20,944.0 (61.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,851.0 (14.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9 (18.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2010
+N = 54,339
 </t>
   </si>
   <si>
-    <t xml:space="preserve">70 (15)</t>
+    <t xml:space="preserve">69.5 (14.8)</t>
   </si>
   <si>
     <t xml:space="preserve">1,659</t>
@@ -257,1603 +259,1684 @@
     <t xml:space="preserve">3,583</t>
   </si>
   <si>
-    <t xml:space="preserve">20,764 (38%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33,575 (62%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,364 (14%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10,573 (19%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10,902 (20%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10,271 (19%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,889 (15%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,340 (14%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">217 (0.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21,558 (40%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38 (&lt;0.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33 (&lt;0.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97 (0.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29,399 (54%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,997 (5.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,530 (12%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18,441 (34%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,425 (16%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20,858 (38%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,036 (15%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18,086 (33%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16,170 (30%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,025 (11%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,022 (11%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34,110 (63%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20,229 (37%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16,300 (30%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37,936 (70%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103 (0.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18,170 (53%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15,863 (47%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77 (0.2%)</t>
+    <t xml:space="preserve">20,764.0 (38.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33,575.0 (61.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,364.0 (13.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10,573.0 (19.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10,902.0 (20.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10,271.0 (18.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,889.0 (14.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,340.0 (13.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">217.0 (0.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21,558.0 (39.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0 (0.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0 (0.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.0 (0.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29,399.0 (54.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,997.0 (5.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,530.0 (12.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18,441.0 (34.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,425.0 (15.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20,858.0 (38.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,036.0 (14.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18,086.0 (33.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16,170.0 (29.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,025.0 (11.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,022.0 (11.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34,110.0 (62.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20,229.0 (37.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16,300.0 (30.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37,936.0 (69.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.0 (0.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18,170.0 (53.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15,863.0 (46.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.0 (0.2%)</t>
   </si>
   <si>
     <t xml:space="preserve">20,229</t>
   </si>
   <si>
-    <t xml:space="preserve">6,315 (19%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,171 (18%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21,624 (63%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,811 (14%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2011, N = 54,144
+    <t xml:space="preserve">6,315.0 (18.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,171.0 (18.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21,624.0 (63.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,811.0 (14.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7 (18.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2011
+N = 54,144
 </t>
   </si>
   <si>
+    <t xml:space="preserve">70.1 (14.9)</t>
+  </si>
+  <si>
     <t xml:space="preserve">1,883</t>
   </si>
   <si>
+    <t xml:space="preserve">165.1 (10.0)</t>
+  </si>
+  <si>
     <t xml:space="preserve">3,537</t>
   </si>
   <si>
-    <t xml:space="preserve">21,426 (40%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32,718 (60%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,971 (13%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10,147 (19%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10,436 (19%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10,359 (19%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,157 (15%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,074 (15%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,433 (2.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22,990 (42%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">857 (1.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55 (0.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">715 (1.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23,174 (43%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,920 (9.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,425 (14%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17,599 (33%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,289 (15%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20,694 (38%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,003 (15%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18,035 (33%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16,085 (30%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,005 (11%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,016 (11%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33,291 (61%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20,853 (39%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16,299 (30%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37,697 (70%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148 (0.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17,202 (52%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16,048 (48%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41 (0.1%)</t>
+    <t xml:space="preserve">21,426.0 (39.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32,718.0 (60.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,971.0 (12.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10,147.0 (18.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10,436.0 (19.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10,359.0 (19.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,157.0 (15.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,074.0 (14.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,433.0 (2.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22,990.0 (42.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">857.0 (1.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.0 (0.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">715.0 (1.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23,174.0 (42.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,920.0 (9.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,425.0 (13.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17,599.0 (32.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,289.0 (15.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20,694.0 (38.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,003.0 (14.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18,035.0 (33.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16,085.0 (29.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,005.0 (11.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,016.0 (11.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33,291.0 (61.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20,853.0 (38.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16,299.0 (30.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37,697.0 (69.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.0 (0.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17,202.0 (51.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16,048.0 (48.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0 (0.1%)</t>
   </si>
   <si>
     <t xml:space="preserve">20,853</t>
   </si>
   <si>
-    <t xml:space="preserve">6,175 (19%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,882 (18%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21,234 (64%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,729 (12%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 (17)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2012, N = 45,448
+    <t xml:space="preserve">6,175.0 (18.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,882.0 (17.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21,234.0 (63.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,729.0 (12.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8 (17.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012
+N = 45,448
 </t>
   </si>
   <si>
+    <t xml:space="preserve">70.5 (14.9)</t>
+  </si>
+  <si>
     <t xml:space="preserve">1,569</t>
   </si>
   <si>
     <t xml:space="preserve">2,921</t>
   </si>
   <si>
-    <t xml:space="preserve">17,389 (38%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28,059 (62%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,353 (12%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,020 (18%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,580 (19%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,723 (19%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,192 (16%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,580 (17%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,228 (2.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18,631 (41%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">771 (1.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167 (0.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,476 (7.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17,296 (38%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,879 (8.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,828 (13%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15,011 (33%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,882 (15%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17,727 (39%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,742 (15%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15,098 (33%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13,500 (30%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,106 (11%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,002 (11%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27,643 (61%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17,805 (39%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12,307 (27%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32,932 (72%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">209 (0.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14,617 (53%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12,950 (47%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76 (0.3%)</t>
+    <t xml:space="preserve">17,389.0 (38.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28,059.0 (61.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,353.0 (11.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,020.0 (17.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,580.0 (18.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,723.0 (19.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,192.0 (15.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,580.0 (16.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,228.0 (2.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18,631.0 (41.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">771.0 (1.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.0 (0.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,476.0 (7.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17,296.0 (38.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,879.0 (8.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,828.0 (12.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15,011.0 (33.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,882.0 (15.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17,727.0 (39.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,742.0 (14.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15,098.0 (33.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13,500.0 (29.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,106.0 (11.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,002.0 (11.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27,643.0 (60.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17,805.0 (39.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12,307.0 (27.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32,932.0 (72.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">209.0 (0.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14,617.0 (52.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12,950.0 (46.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.0 (0.3%)</t>
   </si>
   <si>
     <t xml:space="preserve">17,805</t>
   </si>
   <si>
-    <t xml:space="preserve">4,960 (18%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17,723 (64%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,349 (12%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 (17)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2013, N = 52,929
+    <t xml:space="preserve">4,960.0 (17.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17,723.0 (64.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,349.0 (11.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2 (16.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013
+N = 52,929
 </t>
   </si>
   <si>
-    <t xml:space="preserve">71 (15)</t>
+    <t xml:space="preserve">70.6 (15.0)</t>
   </si>
   <si>
     <t xml:space="preserve">2,040</t>
   </si>
   <si>
+    <t xml:space="preserve">165.0 (10.1)</t>
+  </si>
+  <si>
     <t xml:space="preserve">3,569</t>
   </si>
   <si>
-    <t xml:space="preserve">20,276 (38%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32,653 (62%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,834 (11%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,253 (16%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9,069 (17%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10,004 (19%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9,369 (18%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10,400 (20%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,124 (2.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22,269 (42%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">774 (1.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90 (0.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,899 (9.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19,413 (37%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,360 (8.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,716 (13%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18,506 (35%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,963 (15%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19,501 (37%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,858 (15%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17,613 (33%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15,657 (30%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,945 (11%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,856 (11%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30,573 (58%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22,356 (42%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14,051 (27%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38,459 (73%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419 (0.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15,789 (52%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14,628 (48%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156 (0.5%)</t>
+    <t xml:space="preserve">20,276.0 (38.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32,653.0 (61.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,834.0 (11.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,253.0 (15.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9,069.0 (17.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10,004.0 (18.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9,369.0 (17.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10,400.0 (19.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,124.0 (2.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22,269.0 (42.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">774.0 (1.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.0 (0.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,899.0 (9.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19,413.0 (36.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,360.0 (8.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,716.0 (12.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18,506.0 (35.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,963.0 (15.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19,501.0 (37.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,858.0 (14.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17,613.0 (33.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15,657.0 (29.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,945.0 (11.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,856.0 (11.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30,573.0 (57.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22,356.0 (42.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14,051.0 (26.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38,459.0 (72.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.0 (0.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15,789.0 (51.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14,628.0 (47.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.0 (0.5%)</t>
   </si>
   <si>
     <t xml:space="preserve">22,356</t>
   </si>
   <si>
-    <t xml:space="preserve">5,211 (17%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,763 (16%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20,599 (67%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,962 (9.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 (15)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2014, N = 40,853
+    <t xml:space="preserve">5,211.0 (17.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,763.0 (15.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20,599.0 (67.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,962.0 (9.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9 (15.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014
+N = 40,853
 </t>
   </si>
   <si>
+    <t xml:space="preserve">70.8 (14.9)</t>
+  </si>
+  <si>
     <t xml:space="preserve">1,687</t>
   </si>
   <si>
+    <t xml:space="preserve">164.7 (10.1)</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,876</t>
   </si>
   <si>
-    <t xml:space="preserve">15,521 (38%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25,332 (62%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,316 (11%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,307 (15%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,054 (17%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,656 (19%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,103 (17%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,417 (21%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,045 (2.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16,399 (40%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">568 (1.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117 (0.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,203 (10%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14,928 (37%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,593 (8.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,506 (13%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13,405 (33%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,456 (16%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15,486 (38%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,061 (15%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13,615 (33%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12,077 (30%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,583 (11%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,517 (11%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23,407 (57%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17,446 (43%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10,781 (26%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29,813 (73%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">259 (0.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12,329 (53%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11,008 (47%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70 (0.3%)</t>
+    <t xml:space="preserve">15,521.0 (38.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25,332.0 (62.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,316.0 (10.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,307.0 (15.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,054.0 (17.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,656.0 (18.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,103.0 (17.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,417.0 (20.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,045.0 (2.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16,399.0 (40.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">568.0 (1.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.0 (0.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,203.0 (10.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14,928.0 (36.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,593.0 (8.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,506.0 (13.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13,405.0 (32.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,456.0 (15.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15,486.0 (37.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,061.0 (14.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13,615.0 (33.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12,077.0 (29.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,583.0 (11.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,517.0 (11.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23,407.0 (57.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17,446.0 (42.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10,781.0 (26.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29,813.0 (73.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">259.0 (0.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12,329.0 (52.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11,008.0 (47.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.0 (0.3%)</t>
   </si>
   <si>
     <t xml:space="preserve">17,446</t>
   </si>
   <si>
-    <t xml:space="preserve">4,001 (17%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,761 (16%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15,645 (67%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,839 (9.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2015, N = 54,174
+    <t xml:space="preserve">4,001.0 (17.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,761.0 (16.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15,645.0 (66.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,839.0 (9.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0 (15.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2015
+N = 54,174
 </t>
   </si>
   <si>
+    <t xml:space="preserve">70.9 (14.9)</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,752</t>
   </si>
   <si>
+    <t xml:space="preserve">164.6 (10.1)</t>
+  </si>
+  <si>
     <t xml:space="preserve">4,177</t>
   </si>
   <si>
-    <t xml:space="preserve">20,368 (38%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33,806 (62%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,050 (9.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,163 (13%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,463 (16%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9,750 (18%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10,399 (19%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13,349 (25%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,404 (2.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22,511 (47%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">765 (1.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338 (0.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">809 (1.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18,566 (39%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,441 (7.2%)</t>
+    <t xml:space="preserve">20,368.0 (37.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33,806.0 (62.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,050.0 (9.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,163.0 (13.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,463.0 (15.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9,750.0 (18.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10,399.0 (19.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13,349.0 (24.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,404.0 (2.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22,511.0 (47.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">765.0 (1.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.0 (0.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">809.0 (1.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18,566.0 (38.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,441.0 (7.2%)</t>
   </si>
   <si>
     <t xml:space="preserve">6,340</t>
   </si>
   <si>
-    <t xml:space="preserve">6,943 (13%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19,725 (36%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,981 (15%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19,525 (36%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,023 (15%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18,046 (33%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16,070 (30%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,015 (11%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,020 (11%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28,918 (53%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25,256 (47%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13,360 (25%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40,502 (75%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">312 (0.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15,162 (52%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13,625 (47%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131 (0.5%)</t>
+    <t xml:space="preserve">6,943.0 (12.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19,725.0 (36.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,981.0 (14.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19,525.0 (36.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,023.0 (14.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18,046.0 (33.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16,070.0 (29.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,015.0 (11.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,020.0 (11.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28,918.0 (53.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25,256.0 (46.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13,360.0 (24.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40,502.0 (74.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">312.0 (0.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15,162.0 (52.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13,625.0 (47.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.0 (0.5%)</t>
   </si>
   <si>
     <t xml:space="preserve">25,256</t>
   </si>
   <si>
-    <t xml:space="preserve">5,085 (18%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,276 (15%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19,557 (68%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,817 (8.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 (15)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2016, N = 53,210
+    <t xml:space="preserve">5,085.0 (17.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,276.0 (14.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19,557.0 (67.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,817.0 (8.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4 (14.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016
+N = 53,210
 </t>
   </si>
   <si>
+    <t xml:space="preserve">71.1 (15.0)</t>
+  </si>
+  <si>
     <t xml:space="preserve">1,829</t>
   </si>
   <si>
     <t xml:space="preserve">3,281</t>
   </si>
   <si>
-    <t xml:space="preserve">20,258 (38%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32,952 (62%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,163 (9.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,945 (13%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,925 (15%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9,374 (18%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10,154 (19%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13,649 (26%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">759 (1.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23,300 (44%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">784 (1.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">407 (0.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,812 (7.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20,059 (38%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,089 (7.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,883 (13%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20,729 (39%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,235 (14%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18,363 (35%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,029 (15%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17,792 (33%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15,486 (29%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,971 (11%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,932 (11%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29,785 (56%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23,425 (44%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14,233 (27%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38,958 (73%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19 (&lt;0.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15,966 (54%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13,785 (46%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34 (0.1%)</t>
+    <t xml:space="preserve">20,258.0 (38.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32,952.0 (61.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,163.0 (9.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,945.0 (13.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,925.0 (14.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9,374.0 (17.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10,154.0 (19.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13,649.0 (25.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">759.0 (1.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23,300.0 (43.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">784.0 (1.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">407.0 (0.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,812.0 (7.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20,059.0 (37.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,089.0 (7.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,883.0 (12.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20,729.0 (39.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,235.0 (13.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18,363.0 (34.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,029.0 (15.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17,792.0 (33.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15,486.0 (29.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,971.0 (11.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,932.0 (11.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29,785.0 (56.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23,425.0 (44.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14,233.0 (26.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38,958.0 (73.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0 (0.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15,966.0 (53.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13,785.0 (46.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0 (0.1%)</t>
   </si>
   <si>
     <t xml:space="preserve">23,425</t>
   </si>
   <si>
-    <t xml:space="preserve">4,778 (16%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,829 (16%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20,178 (68%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,442 (10%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 (16)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2017, N = 53,034
+    <t xml:space="preserve">4,778.0 (16.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,829.0 (16.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20,178.0 (67.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,442.0 (10.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1 (15.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017
+N = 53,034
 </t>
   </si>
   <si>
+    <t xml:space="preserve">70.9 (15.0)</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,204</t>
   </si>
   <si>
-    <t xml:space="preserve">164 (10)</t>
+    <t xml:space="preserve">164.4 (10.2)</t>
   </si>
   <si>
     <t xml:space="preserve">3,561</t>
   </si>
   <si>
-    <t xml:space="preserve">19,504 (37%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33,530 (63%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,510 (8.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,000 (11%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,416 (14%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,937 (17%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10,444 (20%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15,727 (30%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">602 (1.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23,250 (48%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">646 (1.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131 (0.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">518 (1.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19,392 (40%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,135 (8.5%)</t>
+    <t xml:space="preserve">19,504.0 (36.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33,530.0 (63.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,510.0 (8.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,000.0 (11.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,416.0 (14.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,937.0 (16.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10,444.0 (19.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15,727.0 (29.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">602.0 (1.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23,250.0 (47.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">646.0 (1.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.0 (0.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">518.0 (1.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19,392.0 (39.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,135.0 (8.5%)</t>
   </si>
   <si>
     <t xml:space="preserve">4,360</t>
   </si>
   <si>
-    <t xml:space="preserve">7,442 (14%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20,462 (39%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,102 (13%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18,028 (34%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,012 (15%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18,382 (35%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14,434 (27%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,106 (12%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,100 (12%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28,392 (54%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24,642 (46%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12,793 (24%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40,204 (76%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37 (&lt;0.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14,928 (53%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13,417 (47%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47 (0.2%)</t>
+    <t xml:space="preserve">7,442.0 (14.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20,462.0 (38.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,102.0 (13.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18,028.0 (34.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,012.0 (15.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18,382.0 (34.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14,434.0 (27.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,106.0 (11.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,100.0 (11.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28,392.0 (53.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24,642.0 (46.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12,793.0 (24.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40,204.0 (75.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0 (0.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14,928.0 (52.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13,417.0 (47.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0 (0.2%)</t>
   </si>
   <si>
     <t xml:space="preserve">24,642</t>
   </si>
   <si>
-    <t xml:space="preserve">4,590 (16%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,035 (14%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19,767 (70%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,898 (9.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2018, N = 52,395
+    <t xml:space="preserve">4,590.0 (16.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,035.0 (14.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19,767.0 (69.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,898.0 (9.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4 (15.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018
+N = 52,395
 </t>
   </si>
   <si>
+    <t xml:space="preserve">71.1 (15.2)</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,180</t>
   </si>
   <si>
+    <t xml:space="preserve">164.3 (10.2)</t>
+  </si>
+  <si>
     <t xml:space="preserve">3,588</t>
   </si>
   <si>
-    <t xml:space="preserve">19,039 (36%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33,356 (64%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,533 (8.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,753 (11%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,438 (14%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,849 (17%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10,484 (20%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15,338 (29%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">452 (0.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22,730 (47%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">585 (1.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65 (0.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431 (0.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19,925 (41%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,957 (8.2%)</t>
+    <t xml:space="preserve">19,039.0 (36.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33,356.0 (63.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,533.0 (8.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,753.0 (11.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,438.0 (14.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,849.0 (16.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10,484.0 (20.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15,338.0 (29.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">452.0 (0.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22,730.0 (47.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">585.0 (1.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.0 (0.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.0 (0.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19,925.0 (41.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,957.0 (8.2%)</t>
   </si>
   <si>
     <t xml:space="preserve">4,250</t>
   </si>
   <si>
-    <t xml:space="preserve">7,817 (15%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20,039 (38%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,735 (13%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17,804 (34%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,149 (16%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18,294 (35%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13,733 (26%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,116 (12%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,103 (12%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27,881 (53%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24,514 (47%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13,481 (26%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38,907 (74%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 (&lt;0.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14,539 (52%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13,307 (48%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35 (0.1%)</t>
+    <t xml:space="preserve">7,817.0 (14.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20,039.0 (38.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,735.0 (12.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17,804.0 (34.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,149.0 (15.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18,294.0 (34.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13,733.0 (26.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,116.0 (11.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,103.0 (11.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27,881.0 (53.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24,514.0 (46.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13,481.0 (25.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38,907.0 (74.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0 (0.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14,539.0 (52.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13,307.0 (47.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0 (0.1%)</t>
   </si>
   <si>
     <t xml:space="preserve">24,514</t>
   </si>
   <si>
-    <t xml:space="preserve">4,305 (15%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,031 (14%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19,545 (70%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,068 (9.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2019, N = 52,443
+    <t xml:space="preserve">4,305.0 (15.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,031.0 (14.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19,545.0 (70.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,068.0 (9.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6 (15.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019
+N = 52,443
 </t>
   </si>
   <si>
+    <t xml:space="preserve">71.0 (15.1)</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,581</t>
   </si>
   <si>
+    <t xml:space="preserve">163.9 (10.2)</t>
+  </si>
+  <si>
     <t xml:space="preserve">3,920</t>
   </si>
   <si>
-    <t xml:space="preserve">18,354 (35%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34,089 (65%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,031 (7.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,052 (9.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,216 (16%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10,618 (20%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17,583 (34%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">427 (0.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22,598 (47%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">617 (1.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53 (0.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">393 (0.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20,217 (42%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,106 (8.5%)</t>
+    <t xml:space="preserve">18,354.0 (35.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34,089.0 (65.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,031.0 (7.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,052.0 (9.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,943.0 (13.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,216.0 (15.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10,618.0 (20.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17,583.0 (33.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">427.0 (0.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22,598.0 (46.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">617.0 (1.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0 (0.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">393.0 (0.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20,217.0 (41.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,106.0 (8.5%)</t>
   </si>
   <si>
     <t xml:space="preserve">4,032</t>
   </si>
   <si>
-    <t xml:space="preserve">8,325 (16%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19,416 (37%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,014 (13%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17,688 (34%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,254 (16%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18,557 (35%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13,274 (25%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,162 (12%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,196 (12%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26,380 (50%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26,063 (50%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12,506 (24%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39,924 (76%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 (&lt;0.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14,009 (53%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12,338 (47%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33 (0.1%)</t>
+    <t xml:space="preserve">8,325.0 (15.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19,416.0 (37.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,014.0 (13.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17,688.0 (33.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,254.0 (15.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18,557.0 (35.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13,274.0 (25.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,162.0 (11.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,196.0 (11.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26,380.0 (50.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26,063.0 (49.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12,506.0 (23.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39,924.0 (76.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0 (0.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14,009.0 (53.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12,338.0 (46.8%)</t>
   </si>
   <si>
     <t xml:space="preserve">26,063</t>
   </si>
   <si>
-    <t xml:space="preserve">4,340 (16%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,988 (15%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18,052 (68%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,127 (9.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020, N = 27,077
+    <t xml:space="preserve">4,340.0 (16.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,988.0 (15.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18,052.0 (68.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,127.0 (9.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7 (15.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020
+N = 27,077
 </t>
   </si>
   <si>
-    <t xml:space="preserve">72 (15)</t>
+    <t xml:space="preserve">71.5 (15.3)</t>
   </si>
   <si>
     <t xml:space="preserve">1,338</t>
   </si>
   <si>
+    <t xml:space="preserve">164.0 (10.1)</t>
+  </si>
+  <si>
     <t xml:space="preserve">1,789</t>
   </si>
   <si>
-    <t xml:space="preserve">9,757 (36%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17,320 (64%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,075 (7.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,726 (10%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,901 (14%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,203 (16%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,231 (19%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,941 (33%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">240 (0.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11,428 (45%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">387 (1.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32 (0.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">199 (0.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11,005 (43%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,169 (8.5%)</t>
+    <t xml:space="preserve">9,757.0 (36.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17,320.0 (64.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,075.0 (7.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,726.0 (10.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,901.0 (14.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,203.0 (15.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,231.0 (19.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,941.0 (33.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240.0 (0.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11,428.0 (44.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">387.0 (1.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">199.0 (0.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11,005.0 (43.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,169.0 (8.5%)</t>
   </si>
   <si>
     <t xml:space="preserve">1,617</t>
   </si>
   <si>
-    <t xml:space="preserve">3,958 (15%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10,321 (38%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,508 (13%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9,290 (34%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,013 (15%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9,013 (33%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,030 (30%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,013 (11%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,008 (11%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13,631 (50%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13,446 (50%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,179 (23%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20,889 (77%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 (&lt;0.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,071 (52%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,547 (48%)</t>
+    <t xml:space="preserve">3,958.0 (14.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10,321.0 (38.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,508.0 (13.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9,290.0 (34.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,013.0 (14.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9,013.0 (33.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,030.0 (29.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,013.0 (11.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,008.0 (11.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13,631.0 (50.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13,446.0 (49.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,179.0 (22.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20,889.0 (77.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0 (0.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,071.0 (51.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,547.0 (48.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0 (0.1%)</t>
   </si>
   <si>
     <t xml:space="preserve">13,446</t>
   </si>
   <si>
-    <t xml:space="preserve">2,204 (16%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,953 (14%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9,474 (70%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,514 (9.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021, N = 27,093
+    <t xml:space="preserve">2,204.0 (16.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,953.0 (14.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9,474.0 (69.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,514.0 (9.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3 (15.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021
+N = 27,093
 </t>
   </si>
   <si>
+    <t xml:space="preserve">71.3 (15.4)</t>
+  </si>
+  <si>
     <t xml:space="preserve">1,428</t>
   </si>
   <si>
-    <t xml:space="preserve">163 (10)</t>
+    <t xml:space="preserve">163.5 (10.2)</t>
   </si>
   <si>
     <t xml:space="preserve">1,787</t>
   </si>
   <si>
-    <t xml:space="preserve">9,271 (34%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17,822 (66%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,717 (6.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,470 (9.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,554 (13%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,880 (14%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,046 (19%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10,426 (38%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">251 (1.0%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11,182 (43%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">292 (1.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115 (0.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">244 (0.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10,851 (42%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,783 (11%)</t>
+    <t xml:space="preserve">9,271.0 (34.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17,822.0 (65.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,717.0 (6.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,470.0 (9.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,554.0 (13.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,880.0 (14.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,046.0 (18.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10,426.0 (38.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">251.0 (1.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11,182.0 (43.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">292.0 (1.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.0 (0.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">244.0 (0.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10,851.0 (42.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,783.0 (10.8%)</t>
   </si>
   <si>
     <t xml:space="preserve">1,375</t>
   </si>
   <si>
-    <t xml:space="preserve">4,212 (16%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10,027 (37%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,705 (14%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9,149 (34%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,007 (15%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9,021 (33%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,022 (30%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,027 (11%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,016 (11%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12,020 (44%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15,073 (56%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,683 (17%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22,400 (83%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 (&lt;0.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,791 (48%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,216 (52%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 (0.1%)</t>
+    <t xml:space="preserve">4,212.0 (15.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10,027.0 (37.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,705.0 (13.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9,149.0 (33.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,007.0 (14.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9,021.0 (33.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,022.0 (29.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,027.0 (11.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,016.0 (11.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12,020.0 (44.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15,073.0 (55.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,683.0 (17.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22,400.0 (82.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0 (0.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,791.0 (48.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,216.0 (51.7%)</t>
   </si>
   <si>
     <t xml:space="preserve">15,073</t>
   </si>
   <si>
-    <t xml:space="preserve">2,141 (18%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,398 (12%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,481 (71%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,983 (7.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (14)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023, N = 21,687
+    <t xml:space="preserve">2,141.0 (17.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,398.0 (11.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,481.0 (70.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,983.0 (7.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0 (13.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023
+N = 21,687
 </t>
   </si>
   <si>
-    <t xml:space="preserve">73 (16)</t>
+    <t xml:space="preserve">73.1 (16.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.6 (10.3)</t>
   </si>
   <si>
     <t xml:space="preserve">1,142</t>
   </si>
   <si>
-    <t xml:space="preserve">8,130 (37%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13,557 (63%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,824 (8.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,214 (15%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,071 (19%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,841 (18%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,665 (17%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,072 (23%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">254 (1.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,043 (38%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">231 (1.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69 (0.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157 (0.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9,998 (47%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,339 (11%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,507 (12%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,069 (37%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,013 (14%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,098 (37%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,204 (15%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,209 (33%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,431 (30%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,427 (11%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,416 (11%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12,278 (57%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9,409 (43%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,396 (25%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16,277 (75%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,760 (47%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,510 (53%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 (&lt;0.1%)</t>
+    <t xml:space="preserve">8,130.0 (37.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13,557.0 (62.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,824.0 (8.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,214.0 (14.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,071.0 (18.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,841.0 (17.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,665.0 (16.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,072.0 (23.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">254.0 (1.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,043.0 (38.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">231.0 (1.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.0 (0.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.0 (0.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9,998.0 (47.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,339.0 (11.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,507.0 (11.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,069.0 (37.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,013.0 (13.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,098.0 (37.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,204.0 (14.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,209.0 (33.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,431.0 (29.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,427.0 (11.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,416.0 (11.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12,278.0 (56.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9,409.0 (43.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,396.0 (24.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16,277.0 (75.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,760.0 (46.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,510.0 (53.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0 (0.1%)</t>
   </si>
   <si>
     <t xml:space="preserve">9,409</t>
   </si>
   <si>
-    <t xml:space="preserve">2,219 (18%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,417 (12%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,642 (70%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,176 (10%)</t>
+    <t xml:space="preserve">2,219.0 (18.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,417.0 (11.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,642.0 (70.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,176.0 (10.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0 (16.1)</t>
   </si>
 </sst>
 </file>
@@ -2318,40 +2401,40 @@
         <v>76</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>446</v>
+        <v>462</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>486</v>
+        <v>505</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>527</v>
+        <v>548</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>570</v>
+        <v>591</v>
       </c>
     </row>
     <row r="2" ht="NA" customHeight="1">
@@ -2365,40 +2448,40 @@
         <v>77</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>77</v>
+        <v>162</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>199</v>
+        <v>246</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>199</v>
+        <v>289</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>199</v>
+        <v>333</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>199</v>
+        <v>375</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>199</v>
+        <v>419</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>199</v>
+        <v>463</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>487</v>
+        <v>506</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>199</v>
+        <v>549</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>571</v>
+        <v>592</v>
       </c>
     </row>
     <row r="3" ht="NA" customHeight="1">
@@ -2412,37 +2495,37 @@
         <v>78</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>447</v>
+        <v>464</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>488</v>
+        <v>507</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>528</v>
+        <v>550</v>
       </c>
       <c r="O3" s="8" t="n">
         <v>819</v>
@@ -2459,40 +2542,40 @@
         <v>35</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>35</v>
+        <v>121</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>35</v>
+        <v>121</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>35</v>
+        <v>205</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>35</v>
+        <v>248</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>35</v>
+        <v>291</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>35</v>
+        <v>291</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>365</v>
+        <v>421</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>365</v>
+        <v>465</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>365</v>
+        <v>508</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>529</v>
+        <v>551</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>35</v>
+        <v>593</v>
       </c>
     </row>
     <row r="5" ht="NA" customHeight="1">
@@ -2506,40 +2589,40 @@
         <v>79</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>407</v>
+        <v>422</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>489</v>
+        <v>509</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>530</v>
+        <v>552</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>572</v>
+        <v>594</v>
       </c>
     </row>
     <row r="6" ht="NA" customHeight="1">
@@ -2600,40 +2683,40 @@
         <v>80</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>408</v>
+        <v>423</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>449</v>
+        <v>467</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>490</v>
+        <v>510</v>
       </c>
       <c r="N7" s="8" t="s">
-        <v>531</v>
+        <v>553</v>
       </c>
       <c r="O7" s="8" t="s">
-        <v>573</v>
+        <v>595</v>
       </c>
     </row>
     <row r="8" ht="NA" customHeight="1">
@@ -2647,40 +2730,40 @@
         <v>81</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>409</v>
+        <v>424</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>450</v>
+        <v>468</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>491</v>
+        <v>511</v>
       </c>
       <c r="N8" s="8" t="s">
-        <v>532</v>
+        <v>554</v>
       </c>
       <c r="O8" s="8" t="s">
-        <v>574</v>
+        <v>596</v>
       </c>
     </row>
     <row r="9" ht="NA" customHeight="1">
@@ -2741,40 +2824,40 @@
         <v>82</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>410</v>
+        <v>425</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>492</v>
+        <v>512</v>
       </c>
       <c r="N10" s="8" t="s">
-        <v>533</v>
+        <v>555</v>
       </c>
       <c r="O10" s="8" t="s">
-        <v>575</v>
+        <v>597</v>
       </c>
     </row>
     <row r="11" ht="NA" customHeight="1">
@@ -2788,40 +2871,40 @@
         <v>83</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>411</v>
+        <v>426</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>452</v>
+        <v>470</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>493</v>
+        <v>513</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>534</v>
+        <v>556</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>576</v>
+        <v>598</v>
       </c>
     </row>
     <row r="12" ht="NA" customHeight="1">
@@ -2835,40 +2918,40 @@
         <v>84</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>412</v>
+        <v>427</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>299</v>
+        <v>471</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>494</v>
+        <v>514</v>
       </c>
       <c r="N12" s="8" t="s">
-        <v>535</v>
+        <v>557</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>577</v>
+        <v>599</v>
       </c>
     </row>
     <row r="13" ht="NA" customHeight="1">
@@ -2882,40 +2965,40 @@
         <v>85</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>413</v>
+        <v>428</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>453</v>
+        <v>472</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>495</v>
+        <v>515</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>536</v>
+        <v>558</v>
       </c>
       <c r="O13" s="8" t="s">
-        <v>578</v>
+        <v>600</v>
       </c>
     </row>
     <row r="14" ht="NA" customHeight="1">
@@ -2929,40 +3012,40 @@
         <v>86</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>414</v>
+        <v>429</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>454</v>
+        <v>473</v>
       </c>
       <c r="M14" s="8" t="s">
-        <v>496</v>
+        <v>516</v>
       </c>
       <c r="N14" s="8" t="s">
-        <v>537</v>
+        <v>559</v>
       </c>
       <c r="O14" s="8" t="s">
-        <v>579</v>
+        <v>601</v>
       </c>
     </row>
     <row r="15" ht="NA" customHeight="1">
@@ -2976,40 +3059,40 @@
         <v>87</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>415</v>
+        <v>430</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>455</v>
+        <v>474</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>497</v>
+        <v>517</v>
       </c>
       <c r="N15" s="8" t="s">
-        <v>538</v>
+        <v>560</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>580</v>
+        <v>602</v>
       </c>
     </row>
     <row r="16" ht="NA" customHeight="1">
@@ -3070,40 +3153,40 @@
         <v>88</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>456</v>
+        <v>475</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>498</v>
+        <v>518</v>
       </c>
       <c r="N17" s="8" t="s">
-        <v>539</v>
+        <v>561</v>
       </c>
       <c r="O17" s="8" t="s">
-        <v>581</v>
+        <v>603</v>
       </c>
     </row>
     <row r="18" ht="NA" customHeight="1">
@@ -3117,40 +3200,40 @@
         <v>89</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>417</v>
+        <v>432</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>457</v>
+        <v>476</v>
       </c>
       <c r="M18" s="8" t="s">
-        <v>499</v>
+        <v>519</v>
       </c>
       <c r="N18" s="8" t="s">
-        <v>540</v>
+        <v>562</v>
       </c>
       <c r="O18" s="8" t="s">
-        <v>582</v>
+        <v>604</v>
       </c>
     </row>
     <row r="19" ht="NA" customHeight="1">
@@ -3164,40 +3247,40 @@
         <v>90</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>418</v>
+        <v>433</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>458</v>
+        <v>477</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="N19" s="8" t="s">
-        <v>541</v>
+        <v>563</v>
       </c>
       <c r="O19" s="8" t="s">
-        <v>583</v>
+        <v>605</v>
       </c>
     </row>
     <row r="20" ht="NA" customHeight="1">
@@ -3211,40 +3294,40 @@
         <v>91</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>419</v>
+        <v>434</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
       <c r="M20" s="8" t="s">
-        <v>501</v>
+        <v>48</v>
       </c>
       <c r="N20" s="8" t="s">
-        <v>542</v>
+        <v>564</v>
       </c>
       <c r="O20" s="8" t="s">
-        <v>584</v>
+        <v>606</v>
       </c>
     </row>
     <row r="21" ht="NA" customHeight="1">
@@ -3258,40 +3341,40 @@
         <v>92</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>460</v>
+        <v>479</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>502</v>
+        <v>521</v>
       </c>
       <c r="N21" s="8" t="s">
-        <v>543</v>
+        <v>565</v>
       </c>
       <c r="O21" s="8" t="s">
-        <v>585</v>
+        <v>607</v>
       </c>
     </row>
     <row r="22" ht="NA" customHeight="1">
@@ -3305,40 +3388,40 @@
         <v>93</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>421</v>
+        <v>436</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>461</v>
+        <v>480</v>
       </c>
       <c r="M22" s="8" t="s">
-        <v>503</v>
+        <v>522</v>
       </c>
       <c r="N22" s="8" t="s">
-        <v>544</v>
+        <v>566</v>
       </c>
       <c r="O22" s="8" t="s">
-        <v>586</v>
+        <v>608</v>
       </c>
     </row>
     <row r="23" ht="NA" customHeight="1">
@@ -3352,40 +3435,40 @@
         <v>94</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>422</v>
+        <v>437</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>462</v>
+        <v>481</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>504</v>
+        <v>523</v>
       </c>
       <c r="N23" s="8" t="s">
-        <v>545</v>
+        <v>567</v>
       </c>
       <c r="O23" s="8" t="s">
-        <v>587</v>
+        <v>609</v>
       </c>
     </row>
     <row r="24" ht="NA" customHeight="1">
@@ -3411,25 +3494,25 @@
         <v>0</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="I24" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>423</v>
+        <v>438</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>463</v>
+        <v>482</v>
       </c>
       <c r="M24" s="8" t="s">
-        <v>505</v>
+        <v>524</v>
       </c>
       <c r="N24" s="8" t="s">
-        <v>546</v>
+        <v>568</v>
       </c>
       <c r="O24" s="8" t="n">
         <v>596</v>
@@ -3493,40 +3576,40 @@
         <v>95</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>464</v>
+        <v>483</v>
       </c>
       <c r="M26" s="8" t="s">
-        <v>506</v>
+        <v>525</v>
       </c>
       <c r="N26" s="8" t="s">
-        <v>547</v>
+        <v>569</v>
       </c>
       <c r="O26" s="8" t="s">
-        <v>588</v>
+        <v>610</v>
       </c>
     </row>
     <row r="27" ht="NA" customHeight="1">
@@ -3540,40 +3623,40 @@
         <v>96</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>465</v>
+        <v>484</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>507</v>
+        <v>526</v>
       </c>
       <c r="N27" s="8" t="s">
-        <v>548</v>
+        <v>570</v>
       </c>
       <c r="O27" s="8" t="s">
-        <v>589</v>
+        <v>611</v>
       </c>
     </row>
     <row r="28" ht="NA" customHeight="1">
@@ -3587,40 +3670,40 @@
         <v>97</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="L28" s="8" t="s">
-        <v>466</v>
+        <v>485</v>
       </c>
       <c r="M28" s="8" t="s">
-        <v>508</v>
+        <v>527</v>
       </c>
       <c r="N28" s="8" t="s">
-        <v>549</v>
+        <v>571</v>
       </c>
       <c r="O28" s="8" t="s">
-        <v>590</v>
+        <v>612</v>
       </c>
     </row>
     <row r="29" ht="NA" customHeight="1">
@@ -3634,40 +3717,40 @@
         <v>98</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="L29" s="8" t="s">
-        <v>467</v>
+        <v>486</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>509</v>
+        <v>528</v>
       </c>
       <c r="N29" s="8" t="s">
-        <v>550</v>
+        <v>572</v>
       </c>
       <c r="O29" s="8" t="s">
-        <v>591</v>
+        <v>613</v>
       </c>
     </row>
     <row r="30" ht="NA" customHeight="1">
@@ -3775,40 +3858,40 @@
         <v>99</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="J32" s="8" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>428</v>
+        <v>443</v>
       </c>
       <c r="L32" s="8" t="s">
-        <v>468</v>
+        <v>487</v>
       </c>
       <c r="M32" s="8" t="s">
-        <v>510</v>
+        <v>529</v>
       </c>
       <c r="N32" s="8" t="s">
-        <v>551</v>
+        <v>573</v>
       </c>
       <c r="O32" s="8" t="s">
-        <v>592</v>
+        <v>614</v>
       </c>
     </row>
     <row r="33" ht="NA" customHeight="1">
@@ -3822,40 +3905,40 @@
         <v>100</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="J33" s="8" t="s">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="K33" s="8" t="s">
-        <v>429</v>
+        <v>444</v>
       </c>
       <c r="L33" s="8" t="s">
-        <v>469</v>
+        <v>488</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>511</v>
+        <v>530</v>
       </c>
       <c r="N33" s="8" t="s">
-        <v>552</v>
+        <v>574</v>
       </c>
       <c r="O33" s="8" t="s">
-        <v>593</v>
+        <v>615</v>
       </c>
     </row>
     <row r="34" ht="NA" customHeight="1">
@@ -3869,40 +3952,40 @@
         <v>101</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="J34" s="8" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="K34" s="8" t="s">
-        <v>430</v>
+        <v>445</v>
       </c>
       <c r="L34" s="8" t="s">
-        <v>470</v>
+        <v>489</v>
       </c>
       <c r="M34" s="8" t="s">
-        <v>512</v>
+        <v>531</v>
       </c>
       <c r="N34" s="8" t="s">
-        <v>553</v>
+        <v>575</v>
       </c>
       <c r="O34" s="8" t="s">
-        <v>594</v>
+        <v>616</v>
       </c>
     </row>
     <row r="35" ht="NA" customHeight="1">
@@ -3916,40 +3999,40 @@
         <v>102</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="K35" s="8" t="s">
-        <v>431</v>
+        <v>446</v>
       </c>
       <c r="L35" s="8" t="s">
-        <v>471</v>
+        <v>490</v>
       </c>
       <c r="M35" s="8" t="s">
-        <v>513</v>
+        <v>532</v>
       </c>
       <c r="N35" s="8" t="s">
-        <v>554</v>
+        <v>576</v>
       </c>
       <c r="O35" s="8" t="s">
-        <v>595</v>
+        <v>617</v>
       </c>
     </row>
     <row r="36" ht="NA" customHeight="1">
@@ -3963,40 +4046,40 @@
         <v>103</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="J36" s="8" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="K36" s="8" t="s">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="L36" s="8" t="s">
-        <v>472</v>
+        <v>491</v>
       </c>
       <c r="M36" s="8" t="s">
-        <v>514</v>
+        <v>533</v>
       </c>
       <c r="N36" s="8" t="s">
-        <v>555</v>
+        <v>577</v>
       </c>
       <c r="O36" s="8" t="s">
-        <v>596</v>
+        <v>618</v>
       </c>
     </row>
     <row r="37" ht="NA" customHeight="1">
@@ -4057,40 +4140,40 @@
         <v>104</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="J38" s="8" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="K38" s="8" t="s">
-        <v>433</v>
+        <v>448</v>
       </c>
       <c r="L38" s="8" t="s">
-        <v>473</v>
+        <v>492</v>
       </c>
       <c r="M38" s="8" t="s">
-        <v>515</v>
+        <v>534</v>
       </c>
       <c r="N38" s="8" t="s">
-        <v>556</v>
+        <v>578</v>
       </c>
       <c r="O38" s="8" t="s">
-        <v>597</v>
+        <v>619</v>
       </c>
     </row>
     <row r="39" ht="NA" customHeight="1">
@@ -4104,40 +4187,40 @@
         <v>105</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="J39" s="8" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="K39" s="8" t="s">
-        <v>434</v>
+        <v>449</v>
       </c>
       <c r="L39" s="8" t="s">
-        <v>474</v>
+        <v>493</v>
       </c>
       <c r="M39" s="8" t="s">
-        <v>516</v>
+        <v>535</v>
       </c>
       <c r="N39" s="8" t="s">
-        <v>557</v>
+        <v>579</v>
       </c>
       <c r="O39" s="8" t="s">
-        <v>598</v>
+        <v>620</v>
       </c>
     </row>
     <row r="40" ht="NA" customHeight="1">
@@ -4198,40 +4281,40 @@
         <v>106</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="J41" s="8" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="K41" s="8" t="s">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="L41" s="8" t="s">
-        <v>475</v>
+        <v>494</v>
       </c>
       <c r="M41" s="8" t="s">
-        <v>517</v>
+        <v>536</v>
       </c>
       <c r="N41" s="8" t="s">
-        <v>558</v>
+        <v>580</v>
       </c>
       <c r="O41" s="8" t="s">
-        <v>599</v>
+        <v>621</v>
       </c>
     </row>
     <row r="42" ht="NA" customHeight="1">
@@ -4245,40 +4328,40 @@
         <v>107</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="I42" s="8" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="J42" s="8" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="K42" s="8" t="s">
-        <v>436</v>
+        <v>451</v>
       </c>
       <c r="L42" s="8" t="s">
-        <v>476</v>
+        <v>495</v>
       </c>
       <c r="M42" s="8" t="s">
-        <v>518</v>
+        <v>537</v>
       </c>
       <c r="N42" s="8" t="s">
-        <v>559</v>
+        <v>581</v>
       </c>
       <c r="O42" s="8" t="s">
-        <v>600</v>
+        <v>622</v>
       </c>
     </row>
     <row r="43" ht="NA" customHeight="1">
@@ -4292,40 +4375,40 @@
         <v>108</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="L43" s="8" t="s">
-        <v>477</v>
+        <v>496</v>
       </c>
       <c r="M43" s="8" t="s">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="N43" s="8" t="s">
-        <v>560</v>
+        <v>582</v>
       </c>
       <c r="O43" s="8" t="s">
-        <v>477</v>
+        <v>541</v>
       </c>
     </row>
     <row r="44" ht="NA" customHeight="1">
@@ -4433,40 +4516,40 @@
         <v>109</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="J46" s="8" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="L46" s="8" t="s">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="M46" s="8" t="s">
-        <v>520</v>
+        <v>539</v>
       </c>
       <c r="N46" s="8" t="s">
-        <v>561</v>
+        <v>583</v>
       </c>
       <c r="O46" s="8" t="s">
-        <v>601</v>
+        <v>623</v>
       </c>
     </row>
     <row r="47" ht="NA" customHeight="1">
@@ -4480,40 +4563,40 @@
         <v>110</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="J47" s="8" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="K47" s="8" t="s">
-        <v>439</v>
+        <v>454</v>
       </c>
       <c r="L47" s="8" t="s">
-        <v>479</v>
+        <v>498</v>
       </c>
       <c r="M47" s="8" t="s">
-        <v>521</v>
+        <v>540</v>
       </c>
       <c r="N47" s="8" t="s">
-        <v>562</v>
+        <v>584</v>
       </c>
       <c r="O47" s="8" t="s">
-        <v>602</v>
+        <v>624</v>
       </c>
     </row>
     <row r="48" ht="NA" customHeight="1">
@@ -4527,40 +4610,40 @@
         <v>111</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="J48" s="8" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="K48" s="8" t="s">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="L48" s="8" t="s">
-        <v>480</v>
+        <v>91</v>
       </c>
       <c r="M48" s="8" t="s">
-        <v>477</v>
+        <v>541</v>
       </c>
       <c r="N48" s="8" t="s">
-        <v>563</v>
+        <v>541</v>
       </c>
       <c r="O48" s="8" t="s">
-        <v>603</v>
+        <v>625</v>
       </c>
     </row>
     <row r="49" ht="NA" customHeight="1">
@@ -4574,40 +4657,40 @@
         <v>112</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="K49" s="8" t="s">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="L49" s="8" t="s">
-        <v>481</v>
+        <v>499</v>
       </c>
       <c r="M49" s="8" t="s">
-        <v>522</v>
+        <v>542</v>
       </c>
       <c r="N49" s="8" t="s">
-        <v>564</v>
+        <v>585</v>
       </c>
       <c r="O49" s="8" t="s">
-        <v>604</v>
+        <v>626</v>
       </c>
     </row>
     <row r="50" ht="NA" customHeight="1">
@@ -4668,40 +4751,40 @@
         <v>113</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="J51" s="8" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="K51" s="8" t="s">
-        <v>442</v>
+        <v>457</v>
       </c>
       <c r="L51" s="8" t="s">
-        <v>482</v>
+        <v>500</v>
       </c>
       <c r="M51" s="8" t="s">
-        <v>523</v>
+        <v>543</v>
       </c>
       <c r="N51" s="8" t="s">
-        <v>565</v>
+        <v>586</v>
       </c>
       <c r="O51" s="8" t="s">
-        <v>605</v>
+        <v>627</v>
       </c>
     </row>
     <row r="52" ht="NA" customHeight="1">
@@ -4715,40 +4798,40 @@
         <v>114</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="J52" s="8" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="K52" s="8" t="s">
-        <v>443</v>
+        <v>458</v>
       </c>
       <c r="L52" s="8" t="s">
-        <v>483</v>
+        <v>501</v>
       </c>
       <c r="M52" s="8" t="s">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="N52" s="8" t="s">
-        <v>566</v>
+        <v>587</v>
       </c>
       <c r="O52" s="8" t="s">
-        <v>606</v>
+        <v>628</v>
       </c>
     </row>
     <row r="53" ht="NA" customHeight="1">
@@ -4762,40 +4845,40 @@
         <v>115</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="J53" s="8" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="K53" s="8" t="s">
-        <v>444</v>
+        <v>459</v>
       </c>
       <c r="L53" s="8" t="s">
-        <v>484</v>
+        <v>502</v>
       </c>
       <c r="M53" s="8" t="s">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="N53" s="8" t="s">
-        <v>567</v>
+        <v>588</v>
       </c>
       <c r="O53" s="8" t="s">
-        <v>607</v>
+        <v>629</v>
       </c>
     </row>
     <row r="54" ht="NA" customHeight="1">
@@ -4809,40 +4892,40 @@
         <v>112</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="J54" s="8" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="K54" s="8" t="s">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="L54" s="8" t="s">
-        <v>481</v>
+        <v>499</v>
       </c>
       <c r="M54" s="8" t="s">
-        <v>522</v>
+        <v>542</v>
       </c>
       <c r="N54" s="8" t="s">
-        <v>564</v>
+        <v>585</v>
       </c>
       <c r="O54" s="8" t="s">
-        <v>604</v>
+        <v>626</v>
       </c>
     </row>
     <row r="55" ht="NA" customHeight="1">
@@ -4856,40 +4939,40 @@
         <v>116</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="J55" s="8" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="K55" s="8" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="L55" s="8" t="s">
-        <v>485</v>
+        <v>503</v>
       </c>
       <c r="M55" s="8" t="s">
-        <v>526</v>
+        <v>546</v>
       </c>
       <c r="N55" s="8" t="s">
-        <v>568</v>
+        <v>589</v>
       </c>
       <c r="O55" s="8" t="s">
-        <v>608</v>
+        <v>630</v>
       </c>
     </row>
     <row r="56" ht="NA" customHeight="1">
@@ -4900,43 +4983,43 @@
         <v>75</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>239</v>
+        <v>287</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="J56" s="9" t="s">
-        <v>321</v>
+        <v>417</v>
       </c>
       <c r="K56" s="9" t="s">
-        <v>239</v>
+        <v>461</v>
       </c>
       <c r="L56" s="9" t="s">
-        <v>362</v>
+        <v>504</v>
       </c>
       <c r="M56" s="9" t="s">
-        <v>321</v>
+        <v>547</v>
       </c>
       <c r="N56" s="9" t="s">
-        <v>569</v>
+        <v>590</v>
       </c>
       <c r="O56" s="9" t="s">
-        <v>362</v>
+        <v>631</v>
       </c>
     </row>
     <row r="57" ht="NA" customHeight="1">
